--- a/public/exports-with-coowners/29189730.xlsx
+++ b/public/exports-with-coowners/29189730.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706715</t>
+          <t xml:space="preserve">311706717</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710301</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -8614,12 +8614,12 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710293</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M115" t="inlineStr">

--- a/public/exports-with-coowners/29189730.xlsx
+++ b/public/exports-with-coowners/29189730.xlsx
@@ -6364,7 +6364,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706717</t>
+          <t xml:space="preserve">311706715</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706709</t>
+          <t xml:space="preserve">311706968</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710303</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710301</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710304</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710306</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -8614,12 +8614,12 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710293</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">

--- a/public/exports-with-coowners/29189730.xlsx
+++ b/public/exports-with-coowners/29189730.xlsx
@@ -7039,7 +7039,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706968</t>
+          <t xml:space="preserve">311706709</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710303</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710304</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710306</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M114" t="inlineStr">
